--- a/autobot/results/birs_successful_taxpayers.xlsx
+++ b/autobot/results/birs_successful_taxpayers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Empty Results" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -401,12 +401,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Status</v>
+        <v>Note</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>No input NINs found. Add NINs to autobot/nins/input.txt</v>
+        <v>No successful verifications found in this run</v>
       </c>
     </row>
   </sheetData>
